--- a/港岛-半山区西部-Mount Pokfulam/Mount Pokfulam_销控明细表.xlsx
+++ b/港岛-半山区西部-Mount Pokfulam/Mount Pokfulam_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,12 +102,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -186,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -236,10 +230,7 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -797,23 +788,19 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>230000000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>47817</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -822,12 +809,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -837,7 +824,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1241,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>1 套</t>
+          <t>0 套</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -1264,7 +1251,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>4 套</t>
+          <t>5 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1335,13 +1322,13 @@
 $43,752/呎</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>薄扶林道86B号
 4810呎 (4+房)
-(在售)
-招标项目
--</t>
+(26年-09月-08日)
+$2.30亿
+$47,817/呎</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
@@ -1371,7 +1358,7 @@
 $41,337/呎</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>薄扶林道86F号
 4717呎 (4+房)
@@ -1380,7 +1367,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>薄扶林道86G号
 3654呎 (4+房)

--- a/港岛-半山区西部-Mount Pokfulam/Mount Pokfulam_销控明细表.xlsx
+++ b/港岛-半山区西部-Mount Pokfulam/Mount Pokfulam_销控明细表.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4810</v>
+        <v>4688</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -793,14 +793,14 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
         <v>230000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>47817</v>
+        <v>49061</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -1325,10 +1325,10 @@
       <c r="C6" s="16" t="inlineStr">
         <is>
           <t>薄扶林道86B号
-4810呎 (4+房)
-(26年-09月-08日)
+4688呎 (4+房)
+(26年-09月-28日)
 $2.30亿
-$47,817/呎</t>
+$49,061/呎</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">

--- a/港岛-半山区西部-Mount Pokfulam/Mount Pokfulam_销控明细表.xlsx
+++ b/港岛-半山区西部-Mount Pokfulam/Mount Pokfulam_销控明细表.xlsx
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3643</v>
+        <v>3724</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>159387200</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>43752</v>
+        <v>42800</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4688</v>
+        <v>4810</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>230000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>49061</v>
+        <v>47817</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>4683</v>
+        <v>4802</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
         <v>230496000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>49220</v>
+        <v>48000</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4578</v>
+        <v>4731</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>189240000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>41337</v>
+        <v>40000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1316,28 +1316,28 @@
       <c r="B6" s="16" t="inlineStr">
         <is>
           <t>薄扶林道86A号
-3643呎 (4+房)
+3724呎 (4+房)
 (25年-09月-18日)
 $1.59亿
-$43,752/呎</t>
+$42,800/呎</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
           <t>薄扶林道86B号
-4688呎 (4+房)
+4810呎 (4+房)
 (26年-09月-28日)
 $2.30亿
-$49,061/呎</t>
+$47,817/呎</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>薄扶林道86C号
-4683呎 (3房)
+4802呎 (3房)
 (25年-04月-30日)
 $2.30亿
-$49,220/呎</t>
+$48,000/呎</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
@@ -1352,10 +1352,10 @@
       <c r="F6" s="16" t="inlineStr">
         <is>
           <t>薄扶林道86E号
-4578呎 (4+房)
+4731呎 (4+房)
 (25年-08月-27日)
 $1.89亿
-$41,337/呎</t>
+$40,000/呎</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
